--- a/data/website_content.xlsx
+++ b/data/website_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\0_Longlong material\longlongWeb\yangcv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53ACD6D-72EC-4129-A6D1-364706E8C9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2882B435-92F1-40E3-887F-CCF26319BC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-105" windowWidth="16440" windowHeight="28320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="profile" sheetId="1" r:id="rId1"/>
@@ -4456,7 +4456,7 @@
         <v>330</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="7"/>
@@ -4484,7 +4484,7 @@
         <v>345</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="7"/>
